--- a/dicionariodedados.xlsx
+++ b/dicionariodedados.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TCC\DD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="156">
   <si>
     <t>ALUNOS</t>
   </si>
@@ -373,6 +373,138 @@
   </si>
   <si>
     <t>DATETIME</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A IDENTIFICAÇÃO DO PEDIDO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR A IDENTIFICAÇÃO DO CAIXA</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR A IDENTIFICAÇÃO DO CLIENTE QUE REALIZOU O PEDIDO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR O STATUS DO PEDIDO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR O VALOR DO PEDIDO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR A DATA E HORA DO PEDIDO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR O TEMPO DE ESPERA DO PEDIDO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR O NÚMERO DA MESA DO PEDIDO</t>
+  </si>
+  <si>
+    <t>ITEID</t>
+  </si>
+  <si>
+    <t>ITEPEDID</t>
+  </si>
+  <si>
+    <t>ITEPROID</t>
+  </si>
+  <si>
+    <t>ITEQUANTIDADE</t>
+  </si>
+  <si>
+    <t>ITEPRECO</t>
+  </si>
+  <si>
+    <t>ITEOBSERVACAO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A IDENTIFICAÇÃO DO ITENS PEDIDO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR A IDENTIFICAÇÃO DO PEDIDO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR A IDENTIFICAÇÃO DO PRODUTO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR A QUANTIDADE DOS ITENS DO PEDIDO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR O PREÇO DOS ITENS DO PEDIDO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR A OBSERVAÇÃO DOS ITENS DO PEDIDO</t>
+  </si>
+  <si>
+    <t>ITENS DO PEDIDOS</t>
+  </si>
+  <si>
+    <t>PAGAMENTOS</t>
+  </si>
+  <si>
+    <t>PAGID</t>
+  </si>
+  <si>
+    <t>PAGPEDID</t>
+  </si>
+  <si>
+    <t>PAGFORMA</t>
+  </si>
+  <si>
+    <t>PAGVALOR</t>
+  </si>
+  <si>
+    <t>PAGDATA_HORA</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A IDENTIFICAÇÃO DO PAGAMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPO DESTINADO A COLOCAR A IDENTIFICAÇÃO DO PEDIDO </t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR A FORMA DE PAGAMENTO(PIX, CRÉDITO, DÉBITO, DINHEIRO)</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR O VALOR DO PAGAMENTO</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR A DATA E HORA DO PAGAMENTO</t>
+  </si>
+  <si>
+    <t>CAIXA</t>
+  </si>
+  <si>
+    <t>CAIID</t>
+  </si>
+  <si>
+    <t>CAIDATA</t>
+  </si>
+  <si>
+    <t>CAITROCO</t>
+  </si>
+  <si>
+    <t>CAITOTAL</t>
+  </si>
+  <si>
+    <t>CAIUSUID</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A IDENTIFICAÇÃO DO CAIXA</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR A DATA DO CAIXA</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR O VALOR DE FECHAMNTO DO CAIXA</t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR O VALOR DE ENTRADA DO CAIXA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPO DESTINADO A COLOCAR A IDENTIFICAÇÃO DO USUÁRIO </t>
+  </si>
+  <si>
+    <t>CAMPO DESTINADO A COLOCAR O TIPO DO PEDIDO (MESA OU RETIRADA)</t>
   </si>
 </sst>
 </file>
@@ -409,7 +541,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,13 +568,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor rgb="FF7BDBCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.249977111117893"/>
+        <fgColor rgb="FF726CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9E0F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,7 +704,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -591,20 +729,37 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -616,28 +771,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -649,6 +783,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,6 +796,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FF726CC8"/>
+      <color rgb="FF7BDBCC"/>
+      <color rgb="FFE9E0F2"/>
       <color rgb="FF66CCFF"/>
       <color rgb="FF22992A"/>
     </mruColors>
@@ -993,165 +1135,165 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="2" spans="1:47">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="F2" s="18" t="s">
+      <c r="D2" s="26"/>
+      <c r="F2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="18"/>
-      <c r="K2" s="18" t="s">
+      <c r="I2" s="23"/>
+      <c r="K2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18" t="s">
+      <c r="L2" s="23"/>
+      <c r="M2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="18"/>
+      <c r="N2" s="23"/>
       <c r="O2" s="1"/>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18" t="s">
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="S2" s="18"/>
-      <c r="U2" s="18" t="s">
+      <c r="S2" s="23"/>
+      <c r="U2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18" t="s">
+      <c r="V2" s="23"/>
+      <c r="W2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="18"/>
-      <c r="Z2" s="18" t="s">
+      <c r="X2" s="23"/>
+      <c r="Z2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18" t="s">
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="18"/>
-      <c r="AE2" s="18" t="s">
+      <c r="AC2" s="23"/>
+      <c r="AE2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="18" t="s">
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" s="18"/>
-      <c r="AJ2" s="18" t="s">
+      <c r="AH2" s="23"/>
+      <c r="AJ2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="21" t="s">
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="AN2" s="18"/>
+      <c r="AN2" s="23"/>
       <c r="AP2" s="6"/>
       <c r="AQ2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="AR2" s="5"/>
-      <c r="AS2" s="18" t="s">
+      <c r="AS2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="AT2" s="18"/>
+      <c r="AT2" s="23"/>
       <c r="AU2" s="1"/>
     </row>
     <row r="3" spans="1:47">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="F3" s="14" t="s">
+      <c r="D3" s="13"/>
+      <c r="F3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14" t="s">
+      <c r="G3" s="13"/>
+      <c r="H3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="K3" s="14" t="s">
+      <c r="I3" s="13"/>
+      <c r="K3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14" t="s">
+      <c r="L3" s="13"/>
+      <c r="M3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="P3" s="14" t="s">
+      <c r="N3" s="13"/>
+      <c r="P3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14" t="s">
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="S3" s="14"/>
-      <c r="U3" s="14" t="s">
+      <c r="S3" s="13"/>
+      <c r="U3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14" t="s">
+      <c r="V3" s="13"/>
+      <c r="W3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="X3" s="14"/>
-      <c r="Z3" s="14" t="s">
+      <c r="X3" s="13"/>
+      <c r="Z3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14" t="s">
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="AC3" s="14"/>
-      <c r="AE3" s="14" t="s">
+      <c r="AC3" s="13"/>
+      <c r="AE3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14" t="s">
+      <c r="AF3" s="13"/>
+      <c r="AG3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="AH3" s="14"/>
-      <c r="AJ3" s="14" t="s">
+      <c r="AH3" s="13"/>
+      <c r="AJ3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AK3" s="14"/>
-      <c r="AL3" s="14"/>
-      <c r="AM3" s="16" t="s">
+      <c r="AK3" s="13"/>
+      <c r="AL3" s="13"/>
+      <c r="AM3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="AN3" s="14"/>
-      <c r="AP3" s="22" t="s">
+      <c r="AN3" s="13"/>
+      <c r="AP3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="AQ3" s="25"/>
-      <c r="AR3" s="23"/>
-      <c r="AS3" s="22" t="s">
+      <c r="AQ3" s="18"/>
+      <c r="AR3" s="19"/>
+      <c r="AS3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="AT3" s="23"/>
+      <c r="AT3" s="19"/>
       <c r="AU3" s="2"/>
     </row>
     <row r="4" spans="1:47">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="14"/>
+      <c r="B4" s="13"/>
       <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
@@ -1160,75 +1302,75 @@
         <v>14</v>
       </c>
       <c r="G4" s="4"/>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="14"/>
-      <c r="K4" s="14" t="s">
+      <c r="I4" s="13"/>
+      <c r="K4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="14"/>
+      <c r="L4" s="13"/>
       <c r="M4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="N4" s="4"/>
-      <c r="P4" s="14" t="s">
+      <c r="P4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="Q4" s="14"/>
+      <c r="Q4" s="13"/>
       <c r="R4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="U4" s="14" t="s">
+      <c r="U4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="V4" s="14"/>
+      <c r="V4" s="13"/>
       <c r="W4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="X4" s="4"/>
-      <c r="Z4" s="14" t="s">
+      <c r="Z4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14" t="s">
+      <c r="AA4" s="13"/>
+      <c r="AB4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="AC4" s="14"/>
-      <c r="AE4" s="14" t="s">
+      <c r="AC4" s="13"/>
+      <c r="AE4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="AF4" s="14"/>
+      <c r="AF4" s="13"/>
       <c r="AG4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="AH4" s="4"/>
-      <c r="AJ4" s="14" t="s">
+      <c r="AJ4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="AK4" s="14"/>
-      <c r="AL4" s="14"/>
-      <c r="AM4" s="16" t="s">
+      <c r="AK4" s="13"/>
+      <c r="AL4" s="13"/>
+      <c r="AM4" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="AN4" s="14"/>
-      <c r="AP4" s="15" t="s">
+      <c r="AN4" s="13"/>
+      <c r="AP4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="AQ4" s="26"/>
-      <c r="AR4" s="16"/>
-      <c r="AS4" s="15" t="s">
+      <c r="AQ4" s="20"/>
+      <c r="AR4" s="15"/>
+      <c r="AS4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="AT4" s="16"/>
+      <c r="AT4" s="15"/>
       <c r="AU4" s="2"/>
     </row>
     <row r="5" spans="1:47">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="14"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
@@ -1237,30 +1379,30 @@
         <v>20</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="14"/>
+      <c r="I5" s="13"/>
       <c r="K5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="4"/>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="14"/>
-      <c r="P5" s="14" t="s">
+      <c r="N5" s="13"/>
+      <c r="P5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="Q5" s="14"/>
+      <c r="Q5" s="13"/>
       <c r="R5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="S5" s="4"/>
-      <c r="U5" s="14" t="s">
+      <c r="U5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="V5" s="14"/>
+      <c r="V5" s="13"/>
       <c r="W5" s="4" t="s">
         <v>21</v>
       </c>
@@ -1269,67 +1411,67 @@
         <v>22</v>
       </c>
       <c r="AA5" s="4"/>
-      <c r="AB5" s="14" t="s">
+      <c r="AB5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="AC5" s="14"/>
-      <c r="AE5" s="14" t="s">
+      <c r="AC5" s="13"/>
+      <c r="AE5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="AF5" s="14"/>
+      <c r="AF5" s="13"/>
       <c r="AG5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="AH5" s="4"/>
-      <c r="AJ5" s="14" t="s">
+      <c r="AJ5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="AK5" s="14"/>
-      <c r="AL5" s="14"/>
-      <c r="AM5" s="16" t="s">
+      <c r="AK5" s="13"/>
+      <c r="AL5" s="13"/>
+      <c r="AM5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="AN5" s="14"/>
-      <c r="AP5" s="15" t="s">
+      <c r="AN5" s="13"/>
+      <c r="AP5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="AQ5" s="26"/>
-      <c r="AR5" s="16"/>
-      <c r="AS5" s="19" t="s">
+      <c r="AQ5" s="20"/>
+      <c r="AR5" s="15"/>
+      <c r="AS5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="AT5" s="20"/>
+      <c r="AT5" s="25"/>
       <c r="AU5" s="3"/>
     </row>
     <row r="6" spans="1:47">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="14"/>
+      <c r="B6" s="13"/>
       <c r="C6" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14" t="s">
+      <c r="G6" s="13"/>
+      <c r="H6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="14"/>
-      <c r="P6" s="14" t="s">
+      <c r="I6" s="13"/>
+      <c r="P6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="Q6" s="14"/>
+      <c r="Q6" s="13"/>
       <c r="R6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="S6" s="4"/>
-      <c r="U6" s="14" t="s">
+      <c r="U6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="V6" s="14"/>
+      <c r="V6" s="13"/>
       <c r="W6" s="4" t="s">
         <v>28</v>
       </c>
@@ -1338,67 +1480,67 @@
         <v>29</v>
       </c>
       <c r="AA6" s="7"/>
-      <c r="AB6" s="14" t="s">
+      <c r="AB6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AC6" s="14"/>
-      <c r="AE6" s="14" t="s">
+      <c r="AC6" s="13"/>
+      <c r="AE6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="AF6" s="14"/>
+      <c r="AF6" s="13"/>
       <c r="AG6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AH6" s="4"/>
-      <c r="AJ6" s="24" t="s">
+      <c r="AJ6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="AK6" s="24"/>
-      <c r="AL6" s="24"/>
-      <c r="AM6" s="27" t="s">
+      <c r="AK6" s="14"/>
+      <c r="AL6" s="14"/>
+      <c r="AM6" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="AN6" s="24"/>
-      <c r="AP6" s="14" t="s">
+      <c r="AN6" s="14"/>
+      <c r="AP6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AQ6" s="14"/>
-      <c r="AR6" s="14"/>
-      <c r="AS6" s="14" t="s">
+      <c r="AQ6" s="13"/>
+      <c r="AR6" s="13"/>
+      <c r="AS6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AT6" s="14"/>
+      <c r="AT6" s="13"/>
       <c r="AU6" s="2"/>
     </row>
     <row r="7" spans="1:47">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="F7" s="14" t="s">
+      <c r="D7" s="15"/>
+      <c r="F7" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14" t="s">
+      <c r="G7" s="13"/>
+      <c r="H7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="14"/>
-      <c r="P7" s="14" t="s">
+      <c r="I7" s="13"/>
+      <c r="P7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="Q7" s="14"/>
+      <c r="Q7" s="13"/>
       <c r="R7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="S7" s="4"/>
-      <c r="U7" s="14" t="s">
+      <c r="U7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="V7" s="14"/>
+      <c r="V7" s="13"/>
       <c r="W7" s="9" t="s">
         <v>21</v>
       </c>
@@ -1407,71 +1549,71 @@
         <v>37</v>
       </c>
       <c r="AA7" s="7"/>
-      <c r="AB7" s="15" t="s">
+      <c r="AB7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="AC7" s="16"/>
-      <c r="AE7" s="24" t="s">
+      <c r="AC7" s="15"/>
+      <c r="AE7" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="AF7" s="24"/>
+      <c r="AF7" s="14"/>
       <c r="AG7" s="11" t="s">
         <v>21</v>
       </c>
       <c r="AH7" s="11"/>
-      <c r="AJ7" s="14" t="s">
+      <c r="AJ7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AK7" s="14"/>
-      <c r="AL7" s="14"/>
-      <c r="AM7" s="14" t="s">
+      <c r="AK7" s="13"/>
+      <c r="AL7" s="13"/>
+      <c r="AM7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AN7" s="14"/>
+      <c r="AN7" s="13"/>
     </row>
     <row r="8" spans="1:47">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="13"/>
       <c r="P8" s="4" t="s">
         <v>41</v>
       </c>
       <c r="Q8" s="4"/>
-      <c r="R8" s="14" t="s">
+      <c r="R8" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="S8" s="14"/>
+      <c r="S8" s="13"/>
       <c r="U8" s="4" t="s">
         <v>41</v>
       </c>
       <c r="V8" s="4"/>
-      <c r="W8" s="14" t="s">
+      <c r="W8" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="X8" s="14"/>
+      <c r="X8" s="13"/>
       <c r="AE8" s="4" t="s">
         <v>41</v>
       </c>
       <c r="AF8" s="4"/>
-      <c r="AG8" s="14" t="s">
+      <c r="AG8" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AH8" s="14"/>
+      <c r="AH8" s="13"/>
     </row>
     <row r="9" spans="1:47">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="14"/>
+      <c r="D9" s="13"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="8"/>
@@ -1481,38 +1623,38 @@
       <c r="AK9" s="2"/>
     </row>
     <row r="10" spans="1:47">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="14"/>
+      <c r="D10" s="13"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
       <c r="S10" s="8"/>
     </row>
     <row r="11" spans="1:47">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14" t="s">
+      <c r="B11" s="13"/>
+      <c r="C11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="14"/>
+      <c r="D11" s="13"/>
     </row>
     <row r="12" spans="1:47">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="13"/>
+      <c r="C12" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="14"/>
+      <c r="D12" s="13"/>
     </row>
     <row r="14" spans="1:47">
       <c r="W14" s="2"/>
@@ -1520,33 +1662,55 @@
     </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AE5:AF5"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AE7:AF7"/>
-    <mergeCell ref="AM4:AN4"/>
-    <mergeCell ref="AS4:AT4"/>
-    <mergeCell ref="AG8:AH8"/>
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AJ5:AL5"/>
-    <mergeCell ref="AJ4:AL4"/>
-    <mergeCell ref="AJ7:AL7"/>
-    <mergeCell ref="AJ6:AL6"/>
-    <mergeCell ref="AS6:AT6"/>
-    <mergeCell ref="AP3:AR3"/>
-    <mergeCell ref="AP4:AR4"/>
-    <mergeCell ref="AP5:AR5"/>
-    <mergeCell ref="AP6:AR6"/>
-    <mergeCell ref="AM6:AN6"/>
-    <mergeCell ref="AM7:AN7"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="AS2:AT2"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM3:AN3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
@@ -1563,55 +1727,33 @@
     <mergeCell ref="AB3:AC3"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AB5:AC5"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="AB7:AC7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="AM2:AN2"/>
+    <mergeCell ref="AS2:AT2"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM3:AN3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AS4:AT4"/>
+    <mergeCell ref="AG8:AH8"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AJ5:AL5"/>
+    <mergeCell ref="AJ4:AL4"/>
+    <mergeCell ref="AJ7:AL7"/>
+    <mergeCell ref="AJ6:AL6"/>
+    <mergeCell ref="AS6:AT6"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="AP4:AR4"/>
+    <mergeCell ref="AP5:AR5"/>
+    <mergeCell ref="AP6:AR6"/>
+    <mergeCell ref="AM6:AN6"/>
+    <mergeCell ref="AM7:AN7"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="AM4:AN4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1619,804 +1761,1283 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J42"/>
+  <dimension ref="B2:J67"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="8" max="8" width="73.625" customWidth="1"/>
+    <col min="8" max="8" width="86.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="31" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="32" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="12"/>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="13"/>
-    </row>
-    <row r="7" spans="2:10">
-      <c r="B7" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="31"/>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" s="12" t="s">
+      <c r="F9" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="32" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="B12" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C18" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D18" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E18" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F18" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G18" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H18" s="31" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
-      <c r="B9" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="7" t="s">
+    <row r="19" spans="2:8">
+      <c r="B19" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="7" t="s">
+      <c r="D19" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="F19" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10">
-      <c r="B10" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="H19" s="32" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D20" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10">
-      <c r="B11" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="F27" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="32" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10">
-      <c r="B12" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="D28" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H29" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="29"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H33" s="31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F34" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G34" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="H34" s="32" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G35" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H35" s="32" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F36" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H36" s="32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G37" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H37" s="32" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G38" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H38" s="32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D39" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H39" s="32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G40" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H40" s="32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H41" s="32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="E42" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F42" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G42" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H42" s="32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="29"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G45" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H45" s="31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D46" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E46" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="F46" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G46" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10">
-      <c r="B14" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10">
-      <c r="B15" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="H46" s="32" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E47" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F47" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="12" t="s">
+      <c r="G47" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H47" s="32" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G48" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H48" s="32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E49" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G49" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H49" s="32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F50" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G50" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H50" s="32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8">
+      <c r="B51" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G51" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H51" s="32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8">
+      <c r="B53" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="29"/>
+    </row>
+    <row r="54" spans="2:8">
+      <c r="B54" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C54" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D54" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E54" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F54" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G54" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H54" s="31" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="7" t="s">
+    <row r="55" spans="2:8">
+      <c r="B55" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C55" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="7" t="s">
+      <c r="D55" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19" s="7" t="s">
+      <c r="F55" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G55" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="7" t="s">
+      <c r="H55" s="32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8">
+      <c r="B56" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E56" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F56" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G56" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H56" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8">
+      <c r="B57" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D57" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E57" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F57" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G57" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H57" s="32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8">
+      <c r="B58" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E58" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F58" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G58" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H58" s="32" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8">
+      <c r="B59" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="D59" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E59" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F59" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G59" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H59" s="32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8">
+      <c r="B61" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="29"/>
+    </row>
+    <row r="62" spans="2:8">
+      <c r="B62" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D62" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="E62" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F62" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G62" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H62" s="31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8">
+      <c r="B63" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C63" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E63" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="7" t="s">
+      <c r="F63" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G63" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="7" t="s">
+      <c r="H63" s="32" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8">
+      <c r="B64" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="C64" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D64" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E64" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F64" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G64" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H64" s="32" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8">
+      <c r="B65" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D65" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E65" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F65" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G65" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H65" s="32" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8">
+      <c r="B66" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C66" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E66" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F66" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G66" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H66" s="32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8">
+      <c r="B67" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="C67" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D67" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E67" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F67" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="31"/>
-    </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H40" s="7"/>
-    </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H41" s="7"/>
-    </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H42" s="7"/>
+      <c r="G67" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H67" s="32" t="s">
+        <v>154</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B61:H61"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B32:H32"/>
     <mergeCell ref="B2:H2"/>
